--- a/SGC-CKN/Excel/b02b4a25-73fd-49c1-8974-b75abc73d76a_Lô_CT-02_P11-29_D800_28-03-2026.xlsx
+++ b/SGC-CKN/Excel/b02b4a25-73fd-49c1-8974-b75abc73d76a_Lô_CT-02_P11-29_D800_28-03-2026.xlsx
@@ -98,11 +98,11 @@
     <t>Sét pha, xám nâu, TT dẻo mềm</t>
   </si>
   <si>
-    <t xml:space="preserve">14:40
+    <t xml:space="preserve">1:40
 27/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">15:30
+    <t xml:space="preserve">2:30
 27/03/2026</t>
   </si>
   <si>
@@ -115,7 +115,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">17:00
+    <t xml:space="preserve">3:00
 27/03/2026</t>
   </si>
   <si>
@@ -125,7 +125,7 @@
     <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
-    <t xml:space="preserve">19:00
+    <t xml:space="preserve">4:00
 27/03/2026</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">21:00
+    <t xml:space="preserve">5:00
 27/03/2026</t>
   </si>
   <si>
@@ -145,7 +145,7 @@
     <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
   </si>
   <si>
-    <t xml:space="preserve">21:30
+    <t xml:space="preserve">5:30
 27/03/2026</t>
   </si>
   <si>
@@ -155,7 +155,7 @@
     <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">22:00
+    <t xml:space="preserve">6:00
 27/03/2026</t>
   </si>
   <si>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:27
-28/03/2026</t>
+27/03/2026</t>
   </si>
   <si>
     <t>Chưa sỏi</t>
@@ -179,7 +179,7 @@
   </si>
   <si>
     <t xml:space="preserve">13:35
-28/03/2026</t>
+27/03/2026</t>
   </si>
   <si>
     <t>Kết thúc</t>
@@ -219,7 +219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -285,12 +285,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF164E63"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -308,7 +302,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -373,11 +367,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -478,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -564,22 +553,19 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1206,13 +1192,13 @@
         <v>-12.9</v>
       </c>
       <c r="H12" s="9">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="9">
         <v>9.09</v>
       </c>
       <c r="J12" s="12">
-        <v>6.06</v>
+        <v>18.18</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1241,13 +1227,13 @@
         <v>-18.2</v>
       </c>
       <c r="H13" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="13">
         <v>5.3</v>
       </c>
-      <c r="J13" s="8">
-        <v>2.65</v>
+      <c r="J13" s="12">
+        <v>5.3</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1276,13 +1262,13 @@
         <v>-28.1</v>
       </c>
       <c r="H14" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="16">
         <v>9.9</v>
       </c>
-      <c r="J14" s="8">
-        <v>4.95</v>
+      <c r="J14" s="12">
+        <v>9.9</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1378,70 +1364,70 @@
         <v>-38.6</v>
       </c>
       <c r="G17" s="25">
-        <v>-44.95</v>
+        <v>-44.45</v>
       </c>
       <c r="H17" s="25">
-        <v>12.45</v>
+        <v>4.45</v>
       </c>
       <c r="I17" s="25">
-        <v>6.35</v>
-      </c>
-      <c r="J17" s="28">
-        <v>0.51</v>
+        <v>5.85</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1.31</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="29">
-        <v>-44.95</v>
-      </c>
-      <c r="G18" s="29">
+      <c r="F18" s="28">
+        <v>-44.45</v>
+      </c>
+      <c r="G18" s="28">
         <v>-49.97</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>3.13</v>
       </c>
-      <c r="I18" s="29">
-        <v>5.02</v>
+      <c r="I18" s="28">
+        <v>5.52</v>
       </c>
       <c r="J18" s="8">
-        <v>1.6</v>
-      </c>
-      <c r="K18" s="30" t="s">
+        <v>1.76</v>
+      </c>
+      <c r="K18" s="29" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1612,13 +1598,13 @@
         <v>-12.9</v>
       </c>
       <c r="G3" s="9">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H3" s="9">
         <v>9.09</v>
       </c>
       <c r="I3" s="12">
-        <v>6.06</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1641,13 +1627,13 @@
         <v>-18.2</v>
       </c>
       <c r="G4" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="13">
         <v>5.3</v>
       </c>
-      <c r="I4" s="8">
-        <v>2.65</v>
+      <c r="I4" s="12">
+        <v>5.3</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1670,13 +1656,13 @@
         <v>-28.1</v>
       </c>
       <c r="G5" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="16">
         <v>9.9</v>
       </c>
-      <c r="I5" s="8">
-        <v>4.95</v>
+      <c r="I5" s="12">
+        <v>9.9</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1754,74 +1740,74 @@
         <v>-38.6</v>
       </c>
       <c r="F8" s="25">
-        <v>-44.95</v>
+        <v>-44.45</v>
       </c>
       <c r="G8" s="25">
-        <v>12.45</v>
+        <v>4.45</v>
       </c>
       <c r="H8" s="25">
-        <v>6.35</v>
-      </c>
-      <c r="I8" s="28">
-        <v>0.51</v>
+        <v>5.85</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1.31</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
-        <v>-44.95</v>
-      </c>
-      <c r="F9" s="29">
+      <c r="E9" s="28">
+        <v>-44.45</v>
+      </c>
+      <c r="F9" s="28">
         <v>-49.97</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>3.13</v>
       </c>
-      <c r="H9" s="29">
-        <v>5.02</v>
+      <c r="H9" s="28">
+        <v>5.52</v>
       </c>
       <c r="I9" s="8">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>-1.07</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>-49.97</v>
       </c>
-      <c r="G10" s="34">
-        <v>22.92</v>
-      </c>
-      <c r="H10" s="34">
+      <c r="G10" s="33">
+        <v>11.92</v>
+      </c>
+      <c r="H10" s="33">
         <v>48.9</v>
       </c>
-      <c r="I10" s="34">
-        <v>2.13</v>
+      <c r="I10" s="33">
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/b02b4a25-73fd-49c1-8974-b75abc73d76a_Lô_CT-02_P11-29_D800_28-03-2026.xlsx
+++ b/SGC-CKN/Excel/b02b4a25-73fd-49c1-8974-b75abc73d76a_Lô_CT-02_P11-29_D800_28-03-2026.xlsx
@@ -98,11 +98,11 @@
     <t>Sét pha, xám nâu, TT dẻo mềm</t>
   </si>
   <si>
-    <t xml:space="preserve">1:40
+    <t xml:space="preserve">01:40
 27/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">2:30
+    <t xml:space="preserve">02:30
 27/03/2026</t>
   </si>
   <si>
@@ -115,7 +115,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">3:00
+    <t xml:space="preserve">03:00
 27/03/2026</t>
   </si>
   <si>
@@ -125,7 +125,7 @@
     <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
-    <t xml:space="preserve">4:00
+    <t xml:space="preserve">04:00
 27/03/2026</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">5:00
+    <t xml:space="preserve">05:00
 27/03/2026</t>
   </si>
   <si>
@@ -145,7 +145,7 @@
     <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
   </si>
   <si>
-    <t xml:space="preserve">5:30
+    <t xml:space="preserve">05:30
 27/03/2026</t>
   </si>
   <si>
@@ -155,7 +155,7 @@
     <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">6:00
+    <t xml:space="preserve">06:00
 27/03/2026</t>
   </si>
   <si>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:27
-27/03/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>Chưa sỏi</t>
@@ -179,7 +179,7 @@
   </si>
   <si>
     <t xml:space="preserve">13:35
-27/03/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>Kết thúc</t>
@@ -219,7 +219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -285,6 +285,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color rgb="FF164E63"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -302,7 +308,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,6 +373,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -467,7 +478,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -553,19 +564,22 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1364,70 +1378,70 @@
         <v>-38.6</v>
       </c>
       <c r="G17" s="25">
-        <v>-44.45</v>
+        <v>-44.95</v>
       </c>
       <c r="H17" s="25">
-        <v>4.45</v>
+        <v>28.45</v>
       </c>
       <c r="I17" s="25">
-        <v>5.85</v>
-      </c>
-      <c r="J17" s="8">
-        <v>1.31</v>
+        <v>6.35</v>
+      </c>
+      <c r="J17" s="28">
+        <v>0.22</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="28">
-        <v>-44.45</v>
-      </c>
-      <c r="G18" s="28">
+      <c r="F18" s="29">
+        <v>-44.95</v>
+      </c>
+      <c r="G18" s="29">
         <v>-49.97</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="29">
         <v>3.13</v>
       </c>
-      <c r="I18" s="28">
-        <v>5.52</v>
+      <c r="I18" s="29">
+        <v>5.02</v>
       </c>
       <c r="J18" s="8">
-        <v>1.76</v>
-      </c>
-      <c r="K18" s="29" t="s">
+        <v>1.6</v>
+      </c>
+      <c r="K18" s="30" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1740,74 +1754,74 @@
         <v>-38.6</v>
       </c>
       <c r="F8" s="25">
-        <v>-44.45</v>
+        <v>-44.95</v>
       </c>
       <c r="G8" s="25">
-        <v>4.45</v>
+        <v>28.45</v>
       </c>
       <c r="H8" s="25">
-        <v>5.85</v>
-      </c>
-      <c r="I8" s="8">
-        <v>1.31</v>
+        <v>6.35</v>
+      </c>
+      <c r="I8" s="28">
+        <v>0.22</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="A9" s="29">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>1</v>
       </c>
-      <c r="E9" s="28">
-        <v>-44.45</v>
-      </c>
-      <c r="F9" s="28">
+      <c r="E9" s="29">
+        <v>-44.95</v>
+      </c>
+      <c r="F9" s="29">
         <v>-49.97</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <v>3.13</v>
       </c>
-      <c r="H9" s="28">
-        <v>5.52</v>
+      <c r="H9" s="29">
+        <v>5.02</v>
       </c>
       <c r="I9" s="8">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <v>8</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="34">
         <v>-1.07</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <v>-49.97</v>
       </c>
-      <c r="G10" s="33">
-        <v>11.92</v>
-      </c>
-      <c r="H10" s="33">
+      <c r="G10" s="34">
+        <v>35.92</v>
+      </c>
+      <c r="H10" s="34">
         <v>48.9</v>
       </c>
-      <c r="I10" s="33">
-        <v>4.1</v>
+      <c r="I10" s="34">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
